--- a/research/traditional_assets/database/data/norway/norway_entertainment.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_entertainment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.289123831775701</v>
+        <v>0.1123550465282749</v>
       </c>
       <c r="H2">
-        <v>-0.298714953271028</v>
+        <v>-0.002891911238367932</v>
       </c>
       <c r="I2">
-        <v>-0.2929906542056075</v>
+        <v>-0.04323550465282749</v>
       </c>
       <c r="J2">
-        <v>-0.2929906542056075</v>
+        <v>-0.04323550465282749</v>
       </c>
       <c r="K2">
-        <v>-46.5</v>
+        <v>-11.3</v>
       </c>
       <c r="L2">
-        <v>-0.5432242990654206</v>
+        <v>-0.08088761632068719</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,58 +627,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>237</v>
+        <v>86.8</v>
       </c>
       <c r="V2">
-        <v>0.08881394041596402</v>
+        <v>0.0892820407323596</v>
+      </c>
+      <c r="W2">
+        <v>-0.02030913012221424</v>
       </c>
       <c r="X2">
-        <v>0.06012249242825989</v>
+        <v>0.1043866904646667</v>
+      </c>
+      <c r="Y2">
+        <v>-0.124695820586881</v>
       </c>
       <c r="AB2">
-        <v>0.05933964872055696</v>
+        <v>0.1041200381608037</v>
       </c>
       <c r="AD2">
-        <v>7.01</v>
+        <v>4.45</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.01</v>
+        <v>4.45</v>
       </c>
       <c r="AG2">
-        <v>-229.99</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.002620061221972633</v>
+        <v>0.004556391747299442</v>
       </c>
       <c r="AI2">
-        <v>0.011375991950796</v>
+        <v>0.007571246278179499</v>
       </c>
       <c r="AJ2">
-        <v>-0.09431579120036415</v>
+        <v>-0.09254368713828172</v>
       </c>
       <c r="AK2">
-        <v>-0.6064977189420112</v>
+        <v>-0.164387663439465</v>
       </c>
       <c r="AL2">
-        <v>0.114</v>
+        <v>0.449</v>
       </c>
       <c r="AM2">
-        <v>-0.511</v>
+        <v>0.164</v>
       </c>
       <c r="AN2">
-        <v>-0.4305896805896806</v>
+        <v>4.944444444444445</v>
       </c>
       <c r="AO2">
-        <v>-220</v>
+        <v>-13.45211581291759</v>
       </c>
       <c r="AP2">
-        <v>14.12714987714988</v>
+        <v>-91.49999999999999</v>
       </c>
       <c r="AQ2">
-        <v>49.08023483365949</v>
+        <v>-36.82926829268292</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.2180140845070423</v>
+        <v>0.1123550465282749</v>
       </c>
       <c r="H3">
-        <v>-0.2295774647887324</v>
+        <v>-0.002891911238367932</v>
       </c>
       <c r="I3">
-        <v>-0.1208450704225352</v>
+        <v>-0.04323550465282749</v>
       </c>
       <c r="J3">
-        <v>-0.1208450704225352</v>
+        <v>-0.04323550465282749</v>
       </c>
       <c r="K3">
-        <v>-26.9</v>
+        <v>-11.3</v>
       </c>
       <c r="L3">
-        <v>-0.3788732394366197</v>
+        <v>-0.08088761632068719</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,168 +743,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>206.4</v>
+        <v>86.8</v>
       </c>
       <c r="V3">
-        <v>0.08019271116636879</v>
+        <v>0.0892820407323596</v>
+      </c>
+      <c r="W3">
+        <v>-0.02030913012221424</v>
       </c>
       <c r="X3">
-        <v>0.05944319490874151</v>
+        <v>0.1043866904646667</v>
+      </c>
+      <c r="Y3">
+        <v>-0.124695820586881</v>
       </c>
       <c r="AB3">
-        <v>0.05939690360531624</v>
+        <v>0.1041200381608037</v>
       </c>
       <c r="AD3">
-        <v>3.17</v>
+        <v>4.45</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.17</v>
+        <v>4.45</v>
       </c>
       <c r="AG3">
-        <v>-203.23</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.001230126854406532</v>
+        <v>0.004556391747299442</v>
       </c>
       <c r="AI3">
-        <v>0.005665064245760138</v>
+        <v>0.007571246278179499</v>
       </c>
       <c r="AJ3">
-        <v>-0.08573043613983135</v>
+        <v>-0.09254368713828172</v>
       </c>
       <c r="AK3">
-        <v>-0.5754452529943088</v>
+        <v>-0.164387663439465</v>
       </c>
       <c r="AL3">
-        <v>0.07199999999999999</v>
+        <v>0.449</v>
       </c>
       <c r="AM3">
-        <v>-0.542</v>
+        <v>0.164</v>
       </c>
       <c r="AN3">
-        <v>-1.331932773109244</v>
+        <v>4.944444444444445</v>
       </c>
       <c r="AO3">
-        <v>-119.1666666666667</v>
+        <v>-13.45211581291759</v>
       </c>
       <c r="AP3">
-        <v>85.39075630252103</v>
+        <v>-91.49999999999999</v>
       </c>
       <c r="AQ3">
-        <v>15.83025830258302</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Play Magnus AS (OB:PMG)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Entertainment</t>
-        </is>
-      </c>
-      <c r="G4">
-        <v>-0.6349315068493151</v>
-      </c>
-      <c r="H4">
-        <v>-0.6349315068493151</v>
-      </c>
-      <c r="I4">
-        <v>-1.13013698630137</v>
-      </c>
-      <c r="J4">
-        <v>-1.13013698630137</v>
-      </c>
-      <c r="K4">
-        <v>-19.6</v>
-      </c>
-      <c r="L4">
-        <v>-1.342465753424658</v>
-      </c>
-      <c r="M4">
-        <v>-0</v>
-      </c>
-      <c r="N4">
-        <v>-0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>30.6</v>
-      </c>
-      <c r="V4">
-        <v>0.3231256599788807</v>
-      </c>
-      <c r="X4">
-        <v>0.06080178994777825</v>
-      </c>
-      <c r="AB4">
-        <v>0.05928239383579767</v>
-      </c>
-      <c r="AD4">
-        <v>3.84</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3.84</v>
-      </c>
-      <c r="AG4">
-        <v>-26.76</v>
-      </c>
-      <c r="AH4">
-        <v>0.03896894662066166</v>
-      </c>
-      <c r="AI4">
-        <v>0.06779661016949153</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3938769502502208</v>
-      </c>
-      <c r="AK4">
-        <v>-1.027649769585254</v>
-      </c>
-      <c r="AL4">
-        <v>0.042</v>
-      </c>
-      <c r="AM4">
-        <v>0.031</v>
-      </c>
-      <c r="AN4">
-        <v>-0.2762589928057554</v>
-      </c>
-      <c r="AO4">
-        <v>-392.8571428571428</v>
-      </c>
-      <c r="AP4">
-        <v>1.925179856115108</v>
-      </c>
-      <c r="AQ4">
-        <v>-532.258064516129</v>
+        <v>-36.82926829268292</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_entertainment.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_entertainment.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1123550465282749</v>
+        <v>0.1653782581055308</v>
       </c>
       <c r="H2">
-        <v>-0.002891911238367932</v>
+        <v>-0.006268277177368086</v>
       </c>
       <c r="I2">
-        <v>-0.04323550465282749</v>
+        <v>-0.03363000635727909</v>
       </c>
       <c r="J2">
-        <v>-0.04323550465282749</v>
+        <v>-0.03363000635727909</v>
       </c>
       <c r="K2">
-        <v>-11.3</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
-        <v>-0.08088761632068719</v>
+        <v>0.03750794659885569</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,70 +621,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>86.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V2">
-        <v>0.0892820407323596</v>
+        <v>0.05811575021056431</v>
       </c>
       <c r="W2">
-        <v>-0.02030913012221424</v>
+        <v>0.01001357773251867</v>
       </c>
       <c r="X2">
-        <v>0.1043866904646667</v>
+        <v>0.08576809554632014</v>
       </c>
       <c r="Y2">
-        <v>-0.124695820586881</v>
+        <v>-0.07575451781380148</v>
+      </c>
+      <c r="Z2">
+        <v>4.851943244910547</v>
+      </c>
+      <c r="AA2">
+        <v>-0.163170882171499</v>
       </c>
       <c r="AB2">
-        <v>0.1041200381608037</v>
+        <v>0.08556376585834533</v>
+      </c>
+      <c r="AC2">
+        <v>-0.2487346480298443</v>
       </c>
       <c r="AD2">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="AG2">
-        <v>-82.34999999999999</v>
+        <v>-89.19999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.004556391747299442</v>
+        <v>0.004432199329180642</v>
       </c>
       <c r="AI2">
-        <v>0.007571246278179499</v>
+        <v>0.01182108626198083</v>
       </c>
       <c r="AJ2">
-        <v>-0.09254368713828172</v>
+        <v>-0.05670692943420216</v>
       </c>
       <c r="AK2">
-        <v>-0.164387663439465</v>
+        <v>-0.168492633169626</v>
       </c>
       <c r="AL2">
-        <v>0.449</v>
+        <v>0.388</v>
       </c>
       <c r="AM2">
-        <v>0.164</v>
+        <v>-1.812</v>
       </c>
       <c r="AN2">
-        <v>4.944444444444445</v>
+        <v>-5.736434108527132</v>
       </c>
       <c r="AO2">
-        <v>-13.45211581291759</v>
+        <v>-13.6340206185567</v>
       </c>
       <c r="AP2">
-        <v>-91.49999999999999</v>
+        <v>69.14728682170542</v>
       </c>
       <c r="AQ2">
-        <v>-36.82926829268292</v>
+        <v>2.919426048565121</v>
       </c>
     </row>
     <row r="3">
@@ -704,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1123550465282749</v>
+        <v>0.1653782581055308</v>
       </c>
       <c r="H3">
-        <v>-0.002891911238367932</v>
+        <v>-0.006268277177368086</v>
       </c>
       <c r="I3">
-        <v>-0.04323550465282749</v>
+        <v>-0.03363000635727909</v>
       </c>
       <c r="J3">
-        <v>-0.04323550465282749</v>
+        <v>-0.03363000635727909</v>
       </c>
       <c r="K3">
-        <v>-11.3</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>-0.08088761632068719</v>
+        <v>0.03750794659885569</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,70 +746,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="V3">
-        <v>0.0892820407323596</v>
+        <v>0.05811575021056431</v>
       </c>
       <c r="W3">
-        <v>-0.02030913012221424</v>
+        <v>0.01001357773251867</v>
       </c>
       <c r="X3">
-        <v>0.1043866904646667</v>
+        <v>0.08576809554632014</v>
       </c>
       <c r="Y3">
-        <v>-0.124695820586881</v>
+        <v>-0.07575451781380148</v>
+      </c>
+      <c r="Z3">
+        <v>4.851943244910547</v>
+      </c>
+      <c r="AA3">
+        <v>-0.163170882171499</v>
       </c>
       <c r="AB3">
-        <v>0.1041200381608037</v>
+        <v>0.08556376585834533</v>
+      </c>
+      <c r="AC3">
+        <v>-0.2487346480298443</v>
       </c>
       <c r="AD3">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.45</v>
+        <v>7.4</v>
       </c>
       <c r="AG3">
-        <v>-82.34999999999999</v>
+        <v>-89.19999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.004556391747299442</v>
+        <v>0.004432199329180642</v>
       </c>
       <c r="AI3">
-        <v>0.007571246278179499</v>
+        <v>0.01182108626198083</v>
       </c>
       <c r="AJ3">
-        <v>-0.09254368713828172</v>
+        <v>-0.05670692943420216</v>
       </c>
       <c r="AK3">
-        <v>-0.164387663439465</v>
+        <v>-0.168492633169626</v>
       </c>
       <c r="AL3">
-        <v>0.449</v>
+        <v>0.388</v>
       </c>
       <c r="AM3">
-        <v>0.164</v>
+        <v>-1.812</v>
       </c>
       <c r="AN3">
-        <v>4.944444444444445</v>
+        <v>-5.736434108527132</v>
       </c>
       <c r="AO3">
-        <v>-13.45211581291759</v>
+        <v>-13.6340206185567</v>
       </c>
       <c r="AP3">
-        <v>-91.49999999999999</v>
+        <v>69.14728682170542</v>
       </c>
       <c r="AQ3">
-        <v>-36.82926829268292</v>
+        <v>2.919426048565121</v>
       </c>
     </row>
   </sheetData>
